--- a/demo_patient_height_cm_single_variable_report.xlsx
+++ b/demo_patient_height_cm_single_variable_report.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.99</v>
       </c>
       <c r="D10" t="n">
-        <v>189.80199999999996</v>
+        <v>189.80200000000005</v>
       </c>
     </row>
     <row r="11" spans="1:4">
